--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487109_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487109_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.6777</v>
+        <v>2.2401</v>
       </c>
       <c r="E2" t="n">
-        <v>2.8855</v>
+        <v>1.662</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7922</v>
+        <v>0.5780999999999999</v>
       </c>
       <c r="G2" t="n">
         <v>-0.8555</v>
@@ -610,13 +610,13 @@
         <v>2.5091</v>
       </c>
       <c r="S2" t="n">
-        <v>2.4404</v>
+        <v>1.0027</v>
       </c>
       <c r="T2" t="n">
-        <v>1.3762</v>
+        <v>0.1527</v>
       </c>
       <c r="U2" t="n">
-        <v>1.0641</v>
+        <v>0.85</v>
       </c>
       <c r="V2" t="n">
         <v>1.5138</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. TEJERINA TEJEDO</t>
+          <t>M. LINDE GIL</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.2228</v>
+        <v>1.925</v>
       </c>
       <c r="E3" t="n">
-        <v>3.21</v>
+        <v>-0.1519</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.9872</v>
+        <v>2.077</v>
       </c>
       <c r="G3" t="n">
-        <v>3.375</v>
+        <v>0.3734</v>
       </c>
       <c r="H3" t="n">
-        <v>1.3693</v>
+        <v>0.4947</v>
       </c>
       <c r="I3" t="n">
-        <v>2.0057</v>
+        <v>-0.1213</v>
       </c>
       <c r="J3" t="n">
-        <v>4.6625</v>
+        <v>2.3682</v>
       </c>
       <c r="K3" t="n">
-        <v>2.0906</v>
+        <v>1.3764</v>
       </c>
       <c r="L3" t="n">
-        <v>2.5719</v>
+        <v>0.9918</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.2875</v>
+        <v>-1.9948</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.7213000000000001</v>
+        <v>-0.8817</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.5662</v>
+        <v>-1.1132</v>
       </c>
       <c r="P3" t="n">
-        <v>0.772</v>
+        <v>-1.158</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.965</v>
+        <v>-3.8602</v>
       </c>
       <c r="R3" t="n">
-        <v>1.7371</v>
+        <v>2.7021</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.7542</v>
+        <v>0.4974</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.7733</v>
+        <v>-0.1738</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0192</v>
+        <v>0.6712</v>
       </c>
       <c r="V3" t="n">
-        <v>-2.1701</v>
+        <v>2.2123</v>
       </c>
       <c r="W3" t="n">
-        <v>0.2859</v>
+        <v>1.5138</v>
       </c>
       <c r="X3" t="n">
-        <v>-2.4559</v>
+        <v>0.6985</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. LINDE GIL</t>
+          <t>J. TEJERINA TEJEDO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9326</v>
+        <v>1.7364</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.3318</v>
+        <v>3.4291</v>
       </c>
       <c r="F4" t="n">
-        <v>2.2643</v>
+        <v>-1.6928</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3734</v>
+        <v>3.375</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4947</v>
+        <v>1.3693</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1213</v>
+        <v>2.0057</v>
       </c>
       <c r="J4" t="n">
-        <v>2.3682</v>
+        <v>4.6625</v>
       </c>
       <c r="K4" t="n">
-        <v>1.3764</v>
+        <v>2.0906</v>
       </c>
       <c r="L4" t="n">
-        <v>0.9918</v>
+        <v>2.5719</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.9948</v>
+        <v>-1.2875</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.8817</v>
+        <v>-0.7213000000000001</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.1132</v>
+        <v>-0.5662</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.158</v>
+        <v>0.772</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3.8602</v>
+        <v>-0.965</v>
       </c>
       <c r="R4" t="n">
-        <v>2.7021</v>
+        <v>1.7371</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.4951</v>
+        <v>-0.2406</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.3537</v>
+        <v>-0.5542</v>
       </c>
       <c r="U4" t="n">
-        <v>0.8586</v>
+        <v>0.3136</v>
       </c>
       <c r="V4" t="n">
-        <v>2.2123</v>
+        <v>-2.1701</v>
       </c>
       <c r="W4" t="n">
-        <v>1.5138</v>
+        <v>0.2859</v>
       </c>
       <c r="X4" t="n">
-        <v>0.6985</v>
+        <v>-2.4559</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5808</v>
+        <v>0.2665</v>
       </c>
       <c r="E5" t="n">
-        <v>1.4301</v>
+        <v>1.3299</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.8492</v>
+        <v>-1.0634</v>
       </c>
       <c r="G5" t="n">
         <v>-1.2514</v>
@@ -844,13 +844,13 @@
         <v>1.3511</v>
       </c>
       <c r="S5" t="n">
-        <v>0.4812</v>
+        <v>0.1669</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1322</v>
+        <v>0.0321</v>
       </c>
       <c r="U5" t="n">
-        <v>0.349</v>
+        <v>0.1348</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>R. ELKSNIS</t>
+          <t>D. CARRETERO GARCIA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.3331</v>
+        <v>0.1565</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5432</v>
+        <v>0.0381</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.8763</v>
+        <v>0.1183</v>
       </c>
       <c r="G6" t="n">
-        <v>-3.0307</v>
+        <v>-0.4501</v>
       </c>
       <c r="H6" t="n">
-        <v>-3.0357</v>
+        <v>-0.1945</v>
       </c>
       <c r="I6" t="n">
-        <v>0.005</v>
+        <v>-0.2556</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.2955</v>
+        <v>0.8637</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.9873</v>
+        <v>0.1397</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6919</v>
+        <v>0.724</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.7353</v>
+        <v>-1.3138</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.0484</v>
+        <v>-0.3341</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.6869</v>
+        <v>-0.9797</v>
       </c>
       <c r="P6" t="n">
-        <v>0.772</v>
+        <v>1.158</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.965</v>
       </c>
       <c r="R6" t="n">
-        <v>0.772</v>
+        <v>2.1231</v>
       </c>
       <c r="S6" t="n">
-        <v>2.5818</v>
+        <v>0.1048</v>
       </c>
       <c r="T6" t="n">
-        <v>2.2091</v>
+        <v>-0.4323</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3728</v>
+        <v>0.537</v>
       </c>
       <c r="V6" t="n">
         <v>-0.6562</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.3704</v>
+        <v>0.5717</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.2859</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. CARRETERO GARCÍA</t>
+          <t>J. CALLENBACH</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,58 +955,58 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.5338000000000001</v>
+        <v>0.102</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0207</v>
+        <v>0.9116</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.5545</v>
+        <v>-0.8095</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.4598</v>
+        <v>-0.6022999999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.1863</v>
+        <v>-0.7472</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2735</v>
+        <v>0.1449</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0207</v>
+        <v>0.7126</v>
       </c>
       <c r="K7" t="n">
         <v>0.0207</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>0.6919</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.4805</v>
+        <v>-1.3149</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.207</v>
+        <v>-0.7679</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.2735</v>
+        <v>-0.5469000000000001</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>0.772</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>0.772</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.074</v>
+        <v>-0.0677</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>0.199</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.074</v>
+        <v>-0.2667</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. CALLENBACH</t>
+          <t>M. CARRETERO GARCÍA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,58 +1033,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.5790999999999999</v>
+        <v>-0.5338000000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3107</v>
+        <v>0.0207</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.8898</v>
+        <v>-0.5545</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.6022999999999999</v>
+        <v>-0.4598</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.7472</v>
+        <v>-0.1863</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1449</v>
+        <v>-0.2735</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7126</v>
+        <v>0.0207</v>
       </c>
       <c r="K8" t="n">
         <v>0.0207</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6919</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.3149</v>
+        <v>-0.4805</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.7679</v>
+        <v>-0.207</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.5469000000000001</v>
+        <v>-0.2735</v>
       </c>
       <c r="P8" t="n">
-        <v>0.772</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.772</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.7489</v>
+        <v>-0.074</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4019</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.347</v>
+        <v>-0.074</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. CARRETERO GARCIA</t>
+          <t>A. RUIZ FERNÁNDEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.6099</v>
+        <v>-0.681</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.5409</v>
+        <v>-0.0188</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.06900000000000001</v>
+        <v>-0.6622</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.4501</v>
+        <v>-0.3062</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.1945</v>
+        <v>-0.207</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2556</v>
+        <v>-0.0993</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8637</v>
+        <v>0.0407</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1397</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0.724</v>
+        <v>0.0407</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.3138</v>
+        <v>-0.3469</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.3341</v>
+        <v>-0.207</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.9797</v>
+        <v>-0.14</v>
       </c>
       <c r="P9" t="n">
-        <v>1.158</v>
+        <v>0.193</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.965</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.1231</v>
+        <v>0.193</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.6617</v>
+        <v>-0.2819</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.0113</v>
+        <v>-0.0595</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3496</v>
+        <v>-0.2224</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.6562</v>
+        <v>-0.2859</v>
       </c>
       <c r="W9" t="n">
-        <v>0.5717</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.228</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. RUIZ FERNÁNDEZ</t>
+          <t>M. SOLORZANO COLSA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.7078</v>
+        <v>-1.4715</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.0188</v>
+        <v>1.078</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.6889999999999999</v>
+        <v>-2.5496</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.3062</v>
+        <v>-2.6514</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.207</v>
+        <v>-1.3247</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.0993</v>
+        <v>-1.3267</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0407</v>
+        <v>0.632</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>0.4449</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0407</v>
+        <v>0.1871</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.3469</v>
+        <v>-3.2834</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.207</v>
+        <v>-1.7697</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.14</v>
+        <v>-1.5137</v>
       </c>
       <c r="P10" t="n">
-        <v>0.193</v>
+        <v>0.386</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-0.965</v>
       </c>
       <c r="R10" t="n">
-        <v>0.193</v>
+        <v>1.3511</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3087</v>
+        <v>0.2221</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0595</v>
+        <v>-0.3886</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2492</v>
+        <v>0.6107</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.2859</v>
+        <v>0.5717</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.7997</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.2859</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. SOLORZANO COLSA</t>
+          <t>R. ELKSNIS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.8047</v>
+        <v>-2.0027</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9591</v>
+        <v>-0.8587</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.7637</v>
+        <v>-1.144</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.6514</v>
+        <v>-3.0307</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.3247</v>
+        <v>-3.0357</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.3267</v>
+        <v>0.005</v>
       </c>
       <c r="J11" t="n">
-        <v>0.632</v>
+        <v>-1.2955</v>
       </c>
       <c r="K11" t="n">
-        <v>0.4449</v>
+        <v>-1.9873</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1871</v>
+        <v>0.6919</v>
       </c>
       <c r="M11" t="n">
-        <v>-3.2834</v>
+        <v>-1.7353</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.7697</v>
+        <v>-1.0484</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.5137</v>
+        <v>-0.6869</v>
       </c>
       <c r="P11" t="n">
-        <v>0.386</v>
+        <v>0.772</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.965</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.3511</v>
+        <v>0.772</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.111</v>
+        <v>0.9122</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5076000000000001</v>
+        <v>0.8071</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3966</v>
+        <v>0.1051</v>
       </c>
       <c r="V11" t="n">
-        <v>0.5717</v>
+        <v>-0.6562</v>
       </c>
       <c r="W11" t="n">
-        <v>1.7997</v>
+        <v>-0.3704</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.228</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.4291</v>
+        <v>-5.4286</v>
       </c>
       <c r="E12" t="n">
-        <v>-7.035</v>
+        <v>-6.1149</v>
       </c>
       <c r="F12" t="n">
-        <v>0.606</v>
+        <v>0.6863</v>
       </c>
       <c r="G12" t="n">
         <v>-5.6887</v>
@@ -1390,13 +1390,13 @@
         <v>2.8951</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.3121</v>
+        <v>-0.3117</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.4872</v>
+        <v>-0.5671</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1751</v>
+        <v>0.2554</v>
       </c>
       <c r="V12" t="n">
         <v>0.5717</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.583600000000001</v>
+        <v>-3.691100000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>0.4328000000000003</v>
+        <v>1.325100000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>-5.0162</v>
+        <v>-5.016299999999999</v>
       </c>
       <c r="G13" t="n">
         <v>-11.5477</v>
@@ -1444,7 +1444,7 @@
         <v>7.802299999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>1.5048</v>
+        <v>1.504799999999999</v>
       </c>
       <c r="L13" t="n">
         <v>6.2978</v>
@@ -1468,13 +1468,13 @@
         <v>16.4057</v>
       </c>
       <c r="S13" t="n">
-        <v>1.0377</v>
+        <v>1.9302</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.877</v>
+        <v>-0.9846000000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>2.9148</v>
+        <v>2.9147</v>
       </c>
       <c r="V13" t="n">
         <v>1.1011</v>
@@ -1483,7 +1483,7 @@
         <v>6.087700000000001</v>
       </c>
       <c r="X13" t="n">
-        <v>-4.986599999999999</v>
+        <v>-4.9866</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>8.852600000000001</v>
+        <v>9.647399999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>7.7581</v>
+        <v>8.258900000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>1.0944</v>
+        <v>1.3886</v>
       </c>
       <c r="G14" t="n">
         <v>7.6988</v>
@@ -1546,13 +1546,13 @@
         <v>1.5441</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.9161</v>
+        <v>-0.1213</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.6993</v>
+        <v>-0.1986</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2168</v>
+        <v>0.07729999999999999</v>
       </c>
       <c r="V14" t="n">
         <v>2.4559</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. FERNANDEZ ORTEGA</t>
+          <t>A. KARATZAS LACABEX</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.6411</v>
+        <v>1.6701</v>
       </c>
       <c r="E15" t="n">
-        <v>3.2931</v>
+        <v>0.2533</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.6519</v>
+        <v>1.4168</v>
       </c>
       <c r="G15" t="n">
-        <v>1.5668</v>
+        <v>4.2373</v>
       </c>
       <c r="H15" t="n">
-        <v>0.8942</v>
+        <v>0.3416</v>
       </c>
       <c r="I15" t="n">
-        <v>0.6726</v>
+        <v>3.8957</v>
       </c>
       <c r="J15" t="n">
-        <v>1.9196</v>
+        <v>4.4165</v>
       </c>
       <c r="K15" t="n">
-        <v>0.4138</v>
+        <v>-0.0519</v>
       </c>
       <c r="L15" t="n">
-        <v>1.5059</v>
+        <v>4.4684</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.3529</v>
+        <v>-0.1792</v>
       </c>
       <c r="N15" t="n">
-        <v>0.4804</v>
+        <v>0.3935</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.8333</v>
+        <v>-0.5727</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.193</v>
+        <v>-2.8951</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.965</v>
+        <v>-4.8252</v>
       </c>
       <c r="R15" t="n">
-        <v>0.772</v>
+        <v>1.9301</v>
       </c>
       <c r="S15" t="n">
-        <v>1.125</v>
+        <v>0.3278</v>
       </c>
       <c r="T15" t="n">
-        <v>1.1105</v>
+        <v>-0.1956</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0145</v>
+        <v>0.5235</v>
       </c>
       <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0.8576</v>
+      </c>
+      <c r="X15" t="n">
         <v>-0.8576</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.228</v>
-      </c>
-      <c r="X15" t="n">
-        <v>-2.0856</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.3351</v>
+        <v>1.4289</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8734</v>
+        <v>0.6731</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4617</v>
+        <v>0.7558</v>
       </c>
       <c r="G16" t="n">
         <v>-0.0393</v>
@@ -1702,13 +1702,13 @@
         <v>0.772</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.3397</v>
+        <v>-0.2459</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1057</v>
+        <v>-0.306</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.234</v>
+        <v>0.0601</v>
       </c>
       <c r="V16" t="n">
         <v>0.9421</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9265</v>
+        <v>1.0144</v>
       </c>
       <c r="E17" t="n">
-        <v>1.7089</v>
+        <v>1.2082</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.7824</v>
+        <v>-0.1938</v>
       </c>
       <c r="G17" t="n">
         <v>1.4529</v>
@@ -1780,13 +1780,13 @@
         <v>1.9301</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.8123</v>
+        <v>-0.7244</v>
       </c>
       <c r="T17" t="n">
-        <v>0.16</v>
+        <v>-0.3407</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.9723000000000001</v>
+        <v>-0.3837</v>
       </c>
       <c r="V17" t="n">
         <v>0.2859</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. KARATZAS LACABEX</t>
+          <t>G. MARTINEZ DE OSABA ANTOLIN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.8425</v>
+        <v>0.6727</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.5478</v>
+        <v>-0.5901</v>
       </c>
       <c r="F18" t="n">
-        <v>1.3903</v>
+        <v>1.2627</v>
       </c>
       <c r="G18" t="n">
-        <v>4.2373</v>
+        <v>1.159</v>
       </c>
       <c r="H18" t="n">
-        <v>0.3416</v>
+        <v>2.3442</v>
       </c>
       <c r="I18" t="n">
-        <v>3.8957</v>
+        <v>-1.1853</v>
       </c>
       <c r="J18" t="n">
-        <v>4.4165</v>
+        <v>0.4576</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.0519</v>
+        <v>0.9624</v>
       </c>
       <c r="L18" t="n">
-        <v>4.4684</v>
+        <v>-0.5048</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.1792</v>
+        <v>0.7014</v>
       </c>
       <c r="N18" t="n">
-        <v>0.3935</v>
+        <v>1.3818</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.5727</v>
+        <v>-0.6805</v>
       </c>
       <c r="P18" t="n">
-        <v>-2.8951</v>
+        <v>-0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-4.8252</v>
+        <v>-0.965</v>
       </c>
       <c r="R18" t="n">
-        <v>1.9301</v>
+        <v>0.965</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4997</v>
+        <v>-0.5708</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.9967</v>
+        <v>-0.08260000000000001</v>
       </c>
       <c r="U18" t="n">
-        <v>0.497</v>
+        <v>-0.4882</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.08450000000000001</v>
       </c>
       <c r="W18" t="n">
-        <v>0.8576</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.8576</v>
+        <v>0.08450000000000001</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>G. MARTINEZ DE OSABA ANTOLIN</t>
+          <t>A. FERNANDEZ ORTEGA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6598000000000001</v>
+        <v>0.6467000000000001</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.7903</v>
+        <v>2.1915</v>
       </c>
       <c r="F19" t="n">
-        <v>1.4501</v>
+        <v>-1.5448</v>
       </c>
       <c r="G19" t="n">
-        <v>1.159</v>
+        <v>1.5668</v>
       </c>
       <c r="H19" t="n">
-        <v>2.3442</v>
+        <v>0.8942</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.1853</v>
+        <v>0.6726</v>
       </c>
       <c r="J19" t="n">
-        <v>0.4576</v>
+        <v>1.9196</v>
       </c>
       <c r="K19" t="n">
-        <v>0.9624</v>
+        <v>0.4138</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.5048</v>
+        <v>1.5059</v>
       </c>
       <c r="M19" t="n">
-        <v>0.7014</v>
+        <v>-0.3529</v>
       </c>
       <c r="N19" t="n">
-        <v>1.3818</v>
+        <v>0.4804</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.6805</v>
+        <v>-0.8333</v>
       </c>
       <c r="P19" t="n">
-        <v>-0</v>
+        <v>-0.193</v>
       </c>
       <c r="Q19" t="n">
         <v>-0.965</v>
       </c>
       <c r="R19" t="n">
-        <v>0.965</v>
+        <v>0.772</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5837</v>
+        <v>0.1305</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2829</v>
+        <v>0.0089</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3008</v>
+        <v>0.1216</v>
       </c>
       <c r="V19" t="n">
-        <v>0.08450000000000001</v>
+        <v>-0.8576</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.228</v>
       </c>
       <c r="X19" t="n">
-        <v>0.08450000000000001</v>
+        <v>-2.0856</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. GUTIEZ SALGADO</t>
+          <t>U. CALVO ARRUZA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,58 +1969,58 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0633</v>
+        <v>-0.8427</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.6074000000000001</v>
+        <v>-0.6827</v>
       </c>
       <c r="F20" t="n">
-        <v>0.5441</v>
+        <v>-0.16</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.9661999999999999</v>
+        <v>-0.9389</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.07870000000000001</v>
+        <v>-0.5662</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.8875</v>
+        <v>-0.3727</v>
       </c>
       <c r="J20" t="n">
-        <v>1.3557</v>
+        <v>-0.5855</v>
       </c>
       <c r="K20" t="n">
-        <v>1.3971</v>
+        <v>-0.6262</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.0414</v>
+        <v>0.0407</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.3219</v>
+        <v>-0.3534</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.4758</v>
+        <v>0.06</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.8461</v>
+        <v>-0.4134</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.772</v>
+        <v>0.193</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.9301</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.158</v>
+        <v>0.193</v>
       </c>
       <c r="S20" t="n">
-        <v>1.6749</v>
+        <v>-0.0968</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.033</v>
+        <v>-0.09719999999999999</v>
       </c>
       <c r="U20" t="n">
-        <v>1.7079</v>
+        <v>0.0003</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>U. CALVO ARRUZA</t>
+          <t>A. GUTIEZ SALGADO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,58 +2047,58 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.1233</v>
+        <v>-0.8922</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.8829</v>
+        <v>-1.008</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.2403</v>
+        <v>0.1158</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.9389</v>
+        <v>-0.9661999999999999</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.5662</v>
+        <v>-0.07870000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3727</v>
+        <v>-0.8875</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.5855</v>
+        <v>1.3557</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.6262</v>
+        <v>1.3971</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0407</v>
+        <v>-0.0414</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.3534</v>
+        <v>-2.3219</v>
       </c>
       <c r="N21" t="n">
-        <v>0.06</v>
+        <v>-1.4758</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.4134</v>
+        <v>-0.8461</v>
       </c>
       <c r="P21" t="n">
-        <v>0.193</v>
+        <v>-0.772</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-1.9301</v>
       </c>
       <c r="R21" t="n">
-        <v>0.193</v>
+        <v>1.158</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3774</v>
+        <v>0.8461</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2974</v>
+        <v>-0.4336</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.08</v>
+        <v>1.2796</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.8019</v>
+        <v>-3.5087</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.3198</v>
+        <v>-3.9193</v>
       </c>
       <c r="F22" t="n">
-        <v>0.518</v>
+        <v>0.4106</v>
       </c>
       <c r="G22" t="n">
         <v>-0.364</v>
@@ -2170,13 +2170,13 @@
         <v>1.158</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1448</v>
+        <v>0.1484</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.2492</v>
+        <v>-0.8487</v>
       </c>
       <c r="U22" t="n">
-        <v>1.1045</v>
+        <v>0.9971</v>
       </c>
       <c r="V22" t="n">
         <v>-1.5561</v>
@@ -2203,10 +2203,10 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.6855</v>
+        <v>-4.5854</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.4688</v>
+        <v>-1.3686</v>
       </c>
       <c r="F23" t="n">
         <v>-3.2167</v>
@@ -2248,10 +2248,10 @@
         <v>1.158</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.1639</v>
+        <v>-0.0638</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5208</v>
+        <v>-0.4207</v>
       </c>
       <c r="U23" t="n">
         <v>0.3569</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>4.5836</v>
+        <v>5.251200000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>5.0165</v>
+        <v>5.0163</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.4327000000000001</v>
+        <v>0.2350000000000003</v>
       </c>
       <c r="G24" t="n">
         <v>11.5477</v>
@@ -2326,16 +2326,16 @@
         <v>11.5803</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.0377</v>
+        <v>-0.3702</v>
       </c>
       <c r="T24" t="n">
-        <v>-2.9145</v>
+        <v>-2.9148</v>
       </c>
       <c r="U24" t="n">
-        <v>1.8769</v>
+        <v>2.5445</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.101200000000001</v>
+        <v>-1.1012</v>
       </c>
       <c r="W24" t="n">
         <v>4.9864</v>
